--- a/delivery130/03_Excel_Deliveries/6_NMAS_Full_Artist_Data_Q1_2019_Q3_2026.xlsx
+++ b/delivery130/03_Excel_Deliveries/6_NMAS_Full_Artist_Data_Q1_2019_Q3_2026.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Matrix_Gross_USD" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Matrix_Gross_USD'!$A$1:$AG$132</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Matrix_Gross_USD'!$A$1:$AG$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Matrix_Gross_USD'!$A$1:$AG$131</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Matrix_Gross_USD'!$A$1:$AG$131</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,14 +468,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Scope: 130 artists (first-submission cohort) x 31 quarters, Q1 2019 – Q3 2026</t>
+          <t>Scope: 129 artists (first-submission cohort) x 31 quarters, Q1 2019 – Q3 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-31. Source: delivery130/04_Datasets — figures equal those cells.</t>
+          <t>Generated 2026-09-01. Source: delivery130/04_Datasets — figures equal those cells.</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AG132"/>
+  <dimension ref="A1:AG131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -515,7 +515,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
@@ -529,9 +529,9 @@
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
     <col width="13" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
     <col width="13" customWidth="1" min="32" max="32"/>
@@ -8953,58 +8953,58 @@
         <v>17145.51</v>
       </c>
       <c r="F86" t="n">
-        <v>17127.09</v>
+        <v>17094.93</v>
       </c>
       <c r="G86" t="n">
-        <v>23181.78</v>
+        <v>23128.09</v>
       </c>
       <c r="H86" t="n">
-        <v>19557.3</v>
+        <v>19488.37</v>
       </c>
       <c r="I86" t="n">
-        <v>18164.53</v>
+        <v>18085.04</v>
       </c>
       <c r="J86" t="n">
-        <v>18721.33</v>
+        <v>18631.52</v>
       </c>
       <c r="K86" t="n">
-        <v>20443.23</v>
+        <v>20345.14</v>
       </c>
       <c r="L86" t="n">
-        <v>19743.11</v>
+        <v>19636.91</v>
       </c>
       <c r="M86" t="n">
-        <v>22749.57</v>
+        <v>22637.42</v>
       </c>
       <c r="N86" t="n">
-        <v>25376.06</v>
+        <v>25258</v>
       </c>
       <c r="O86" t="n">
-        <v>26764.77</v>
+        <v>26642.87</v>
       </c>
       <c r="P86" t="n">
-        <v>27644.61</v>
+        <v>27520.82</v>
       </c>
       <c r="Q86" t="n">
-        <v>21919.03</v>
+        <v>21793.51</v>
       </c>
       <c r="R86" t="n">
-        <v>23300.05</v>
+        <v>23173.26</v>
       </c>
       <c r="S86" t="n">
-        <v>21893.4</v>
+        <v>21765.91</v>
       </c>
       <c r="T86" t="n">
-        <v>20041.08</v>
+        <v>19913.04</v>
       </c>
       <c r="U86" t="n">
-        <v>18070.42</v>
+        <v>17941.83</v>
       </c>
       <c r="V86" t="n">
-        <v>20571.38</v>
+        <v>20442.28</v>
       </c>
       <c r="W86" t="n">
-        <v>21000.16</v>
+        <v>20870.58</v>
       </c>
       <c r="X86" t="n">
         <v>19857.03</v>
@@ -9028,13 +9028,13 @@
         <v>13478.78</v>
       </c>
       <c r="AE86" t="n">
-        <v>17025.74</v>
+        <v>16888.75</v>
       </c>
       <c r="AF86" t="n">
-        <v>15726.93</v>
+        <v>15588.98</v>
       </c>
       <c r="AG86" s="4" t="n">
-        <v>604469.79</v>
+        <v>602295.47</v>
       </c>
     </row>
     <row r="87">
@@ -13395,199 +13395,108 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Odunsi</t>
-        </is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1872809.25</v>
+      </c>
+      <c r="C131" t="n">
+        <v>2323531.26</v>
+      </c>
+      <c r="D131" t="n">
+        <v>3218095.33</v>
+      </c>
+      <c r="E131" t="n">
+        <v>4262610.88</v>
       </c>
       <c r="F131" t="n">
-        <v>0.22</v>
+        <v>3987655.09</v>
       </c>
       <c r="G131" t="n">
-        <v>0.24</v>
+        <v>4568628.61</v>
       </c>
       <c r="H131" t="n">
-        <v>0.26</v>
+        <v>5247193.78</v>
       </c>
       <c r="I131" t="n">
-        <v>0.26</v>
+        <v>5432177.22</v>
       </c>
       <c r="J131" t="n">
-        <v>0.26</v>
+        <v>5875850.44</v>
       </c>
       <c r="K131" t="n">
-        <v>0.26</v>
+        <v>6942911.89</v>
       </c>
       <c r="L131" t="n">
-        <v>0.29</v>
+        <v>8947551.25</v>
       </c>
       <c r="M131" t="n">
-        <v>0.31</v>
+        <v>12461372.1</v>
       </c>
       <c r="N131" t="n">
-        <v>0.31</v>
+        <v>12521951.57</v>
       </c>
       <c r="O131" t="n">
-        <v>0.31</v>
+        <v>13725097.33</v>
       </c>
       <c r="P131" t="n">
-        <v>0.31</v>
+        <v>16545709.43</v>
       </c>
       <c r="Q131" t="n">
-        <v>0.31</v>
+        <v>17741765.98</v>
       </c>
       <c r="R131" t="n">
-        <v>0.31</v>
+        <v>19660200.27</v>
       </c>
       <c r="S131" t="n">
-        <v>0.31</v>
+        <v>23324850.92</v>
       </c>
       <c r="T131" t="n">
-        <v>0.31</v>
+        <v>20941810.56</v>
       </c>
       <c r="U131" t="n">
-        <v>0.31</v>
+        <v>21429687.92</v>
       </c>
       <c r="V131" t="n">
-        <v>0.31</v>
+        <v>20850157.48</v>
       </c>
       <c r="W131" t="n">
-        <v>0.31</v>
+        <v>23032018.33</v>
       </c>
       <c r="X131" t="n">
-        <v>0.31</v>
+        <v>23051208.35</v>
       </c>
       <c r="Y131" t="n">
-        <v>0.31</v>
+        <v>23152245.93</v>
       </c>
       <c r="Z131" t="n">
-        <v>0.31</v>
+        <v>20985647.25</v>
       </c>
       <c r="AA131" t="n">
-        <v>0.31</v>
+        <v>24001481.19</v>
       </c>
       <c r="AB131" t="n">
-        <v>0.31</v>
+        <v>23834738.27</v>
       </c>
       <c r="AC131" t="n">
-        <v>0.31</v>
+        <v>24891805.4</v>
       </c>
       <c r="AD131" t="n">
-        <v>0.31</v>
+        <v>25010047.72</v>
       </c>
       <c r="AE131" t="n">
-        <v>0.31</v>
+        <v>28565091.87</v>
       </c>
       <c r="AF131" t="n">
-        <v>0.31</v>
+        <v>28556131.57</v>
       </c>
       <c r="AG131" s="4" t="n">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>=== PERIOD TOTAL ===</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>1872809.25</v>
-      </c>
-      <c r="C132" t="n">
-        <v>2323531.26</v>
-      </c>
-      <c r="D132" t="n">
-        <v>3218095.33</v>
-      </c>
-      <c r="E132" t="n">
-        <v>4262610.88</v>
-      </c>
-      <c r="F132" t="n">
-        <v>3987687.47</v>
-      </c>
-      <c r="G132" t="n">
-        <v>4568682.54</v>
-      </c>
-      <c r="H132" t="n">
-        <v>5247262.97</v>
-      </c>
-      <c r="I132" t="n">
-        <v>5432256.97</v>
-      </c>
-      <c r="J132" t="n">
-        <v>5875940.51</v>
-      </c>
-      <c r="K132" t="n">
-        <v>6943010.24</v>
-      </c>
-      <c r="L132" t="n">
-        <v>8947657.74</v>
-      </c>
-      <c r="M132" t="n">
-        <v>12461484.56</v>
-      </c>
-      <c r="N132" t="n">
-        <v>12522069.94</v>
-      </c>
-      <c r="O132" t="n">
-        <v>13725219.54</v>
-      </c>
-      <c r="P132" t="n">
-        <v>16545833.53</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>17741891.81</v>
-      </c>
-      <c r="R132" t="n">
-        <v>19660327.37</v>
-      </c>
-      <c r="S132" t="n">
-        <v>23324978.72</v>
-      </c>
-      <c r="T132" t="n">
-        <v>20941938.91</v>
-      </c>
-      <c r="U132" t="n">
-        <v>21429816.82</v>
-      </c>
-      <c r="V132" t="n">
-        <v>20850286.89</v>
-      </c>
-      <c r="W132" t="n">
-        <v>23032148.22</v>
-      </c>
-      <c r="X132" t="n">
-        <v>23051208.66</v>
-      </c>
-      <c r="Y132" t="n">
-        <v>23152246.24</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>20985647.56</v>
-      </c>
-      <c r="AA132" t="n">
-        <v>24001481.5</v>
-      </c>
-      <c r="AB132" t="n">
-        <v>23834738.58</v>
-      </c>
-      <c r="AC132" t="n">
-        <v>24891805.71</v>
-      </c>
-      <c r="AD132" t="n">
-        <v>25010048.03</v>
-      </c>
-      <c r="AE132" t="n">
-        <v>28565229.17</v>
-      </c>
-      <c r="AF132" t="n">
-        <v>28556269.83</v>
-      </c>
-      <c r="AG132" s="4" t="n">
-        <v>476964216.75</v>
+        <v>476962034.44</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG132"/>
+  <autoFilter ref="A1:AG131"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/delivery130/03_Excel_Deliveries/6_NMAS_Full_Artist_Data_Q1_2019_Q3_2026.xlsx
+++ b/delivery130/03_Excel_Deliveries/6_NMAS_Full_Artist_Data_Q1_2019_Q3_2026.xlsx
@@ -509,20 +509,20 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
@@ -531,7 +531,7 @@
     <col width="13" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
     <col width="13" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
     <col width="13" customWidth="1" min="32" max="32"/>
@@ -2221,7 +2221,7 @@
         <v>261084.18</v>
       </c>
       <c r="I17" t="n">
-        <v>251248.62</v>
+        <v>269691.63</v>
       </c>
       <c r="J17" t="n">
         <v>289559.66</v>
@@ -2236,7 +2236,7 @@
         <v>243189.74</v>
       </c>
       <c r="N17" t="n">
-        <v>185725.67</v>
+        <v>212633.91</v>
       </c>
       <c r="O17" t="n">
         <v>201973.82</v>
@@ -2269,7 +2269,7 @@
         <v>208854.3</v>
       </c>
       <c r="Y17" t="n">
-        <v>215543.39</v>
+        <v>217509.32</v>
       </c>
       <c r="Z17" t="n">
         <v>172752.29</v>
@@ -2281,7 +2281,7 @@
         <v>360436.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>382997.87</v>
+        <v>289878.08</v>
       </c>
       <c r="AD17" t="n">
         <v>224924.95</v>
@@ -2293,7 +2293,7 @@
         <v>375034.23</v>
       </c>
       <c r="AG17" s="4" t="n">
-        <v>7216616.46</v>
+        <v>7170813.85</v>
       </c>
     </row>
     <row r="18">
@@ -8953,58 +8953,58 @@
         <v>17145.51</v>
       </c>
       <c r="F86" t="n">
-        <v>17094.93</v>
+        <v>17127.09</v>
       </c>
       <c r="G86" t="n">
-        <v>23128.09</v>
+        <v>23181.78</v>
       </c>
       <c r="H86" t="n">
-        <v>19488.37</v>
+        <v>19557.3</v>
       </c>
       <c r="I86" t="n">
-        <v>18085.04</v>
+        <v>18164.53</v>
       </c>
       <c r="J86" t="n">
-        <v>18631.52</v>
+        <v>18721.33</v>
       </c>
       <c r="K86" t="n">
-        <v>20345.14</v>
+        <v>20443.23</v>
       </c>
       <c r="L86" t="n">
-        <v>19636.91</v>
+        <v>19743.11</v>
       </c>
       <c r="M86" t="n">
-        <v>22637.42</v>
+        <v>22749.57</v>
       </c>
       <c r="N86" t="n">
-        <v>25258</v>
+        <v>25376.06</v>
       </c>
       <c r="O86" t="n">
-        <v>26642.87</v>
+        <v>26764.77</v>
       </c>
       <c r="P86" t="n">
-        <v>27520.82</v>
+        <v>27644.61</v>
       </c>
       <c r="Q86" t="n">
-        <v>21793.51</v>
+        <v>21919.03</v>
       </c>
       <c r="R86" t="n">
-        <v>23173.26</v>
+        <v>23300.05</v>
       </c>
       <c r="S86" t="n">
-        <v>21765.91</v>
+        <v>21893.4</v>
       </c>
       <c r="T86" t="n">
-        <v>19913.04</v>
+        <v>20041.08</v>
       </c>
       <c r="U86" t="n">
-        <v>17941.83</v>
+        <v>18070.42</v>
       </c>
       <c r="V86" t="n">
-        <v>20442.28</v>
+        <v>20571.38</v>
       </c>
       <c r="W86" t="n">
-        <v>20870.58</v>
+        <v>21000.16</v>
       </c>
       <c r="X86" t="n">
         <v>19857.03</v>
@@ -9028,13 +9028,13 @@
         <v>13478.78</v>
       </c>
       <c r="AE86" t="n">
-        <v>16888.75</v>
+        <v>17025.74</v>
       </c>
       <c r="AF86" t="n">
-        <v>15588.98</v>
+        <v>15726.93</v>
       </c>
       <c r="AG86" s="4" t="n">
-        <v>602295.47</v>
+        <v>604469.79</v>
       </c>
     </row>
     <row r="87">
@@ -13411,64 +13411,64 @@
         <v>4262610.88</v>
       </c>
       <c r="F131" t="n">
-        <v>3987655.09</v>
+        <v>3987687.25</v>
       </c>
       <c r="G131" t="n">
-        <v>4568628.61</v>
+        <v>4568682.3</v>
       </c>
       <c r="H131" t="n">
-        <v>5247193.78</v>
+        <v>5247262.71</v>
       </c>
       <c r="I131" t="n">
-        <v>5432177.22</v>
+        <v>5450699.72</v>
       </c>
       <c r="J131" t="n">
-        <v>5875850.44</v>
+        <v>5875940.25</v>
       </c>
       <c r="K131" t="n">
-        <v>6942911.89</v>
+        <v>6943009.98</v>
       </c>
       <c r="L131" t="n">
-        <v>8947551.25</v>
+        <v>8947657.449999999</v>
       </c>
       <c r="M131" t="n">
-        <v>12461372.1</v>
+        <v>12461484.25</v>
       </c>
       <c r="N131" t="n">
-        <v>12521951.57</v>
+        <v>12548977.87</v>
       </c>
       <c r="O131" t="n">
-        <v>13725097.33</v>
+        <v>13725219.23</v>
       </c>
       <c r="P131" t="n">
-        <v>16545709.43</v>
+        <v>16545833.22</v>
       </c>
       <c r="Q131" t="n">
-        <v>17741765.98</v>
+        <v>17741891.5</v>
       </c>
       <c r="R131" t="n">
-        <v>19660200.27</v>
+        <v>19660327.06</v>
       </c>
       <c r="S131" t="n">
-        <v>23324850.92</v>
+        <v>23324978.41</v>
       </c>
       <c r="T131" t="n">
-        <v>20941810.56</v>
+        <v>20941938.6</v>
       </c>
       <c r="U131" t="n">
-        <v>21429687.92</v>
+        <v>21429816.51</v>
       </c>
       <c r="V131" t="n">
-        <v>20850157.48</v>
+        <v>20850286.58</v>
       </c>
       <c r="W131" t="n">
-        <v>23032018.33</v>
+        <v>23032147.91</v>
       </c>
       <c r="X131" t="n">
         <v>23051208.35</v>
       </c>
       <c r="Y131" t="n">
-        <v>23152245.93</v>
+        <v>23154211.86</v>
       </c>
       <c r="Z131" t="n">
         <v>20985647.25</v>
@@ -13480,19 +13480,19 @@
         <v>23834738.27</v>
       </c>
       <c r="AC131" t="n">
-        <v>24891805.4</v>
+        <v>24798685.61</v>
       </c>
       <c r="AD131" t="n">
         <v>25010047.72</v>
       </c>
       <c r="AE131" t="n">
-        <v>28565091.87</v>
+        <v>28565228.86</v>
       </c>
       <c r="AF131" t="n">
-        <v>28556131.57</v>
+        <v>28556269.52</v>
       </c>
       <c r="AG131" s="4" t="n">
-        <v>476962034.44</v>
+        <v>476918406.15</v>
       </c>
     </row>
   </sheetData>
